--- a/jira_automation/project_documents.xlsx
+++ b/jira_automation/project_documents.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{B6C0A815-73DE-4EE5-BB78-ACDE8A38568F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" firstSheet="88" activeTab="91" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" tabRatio="881" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="HomePage" sheetId="1" r:id="rId1"/>
@@ -101,8 +100,7 @@
     <sheet name="PageNotFoundPage" sheetId="91" r:id="rId91"/>
     <sheet name="WildcardNotFoundPage" sheetId="92" r:id="rId92"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <oleSize ref="A1:L31"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -721,8 +719,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1086,9 +1084,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -1096,21 +1094,21 @@
     <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>114</v>
       </c>
@@ -1130,31 +1128,31 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>123</v>
       </c>
@@ -1174,31 +1172,31 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>124</v>
       </c>
@@ -1218,31 +1216,31 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>125</v>
       </c>
@@ -1262,31 +1260,31 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>126</v>
       </c>
@@ -1306,31 +1304,31 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>127</v>
       </c>
@@ -1350,31 +1348,31 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>128</v>
       </c>
@@ -1394,31 +1392,31 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>129</v>
       </c>
@@ -1438,31 +1436,31 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>130</v>
       </c>
@@ -1482,31 +1480,31 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>131</v>
       </c>
@@ -1526,31 +1524,31 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>132</v>
       </c>
@@ -1570,31 +1568,31 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
         <v>115</v>
       </c>
@@ -1614,31 +1612,31 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>133</v>
       </c>
@@ -1658,31 +1656,31 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>134</v>
       </c>
@@ -1702,31 +1700,31 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>135</v>
       </c>
@@ -1746,31 +1744,31 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>136</v>
       </c>
@@ -1790,31 +1788,31 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>137</v>
       </c>
@@ -1834,31 +1832,31 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>138</v>
       </c>
@@ -1878,31 +1876,31 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1900-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>139</v>
       </c>
@@ -1922,31 +1920,31 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1A00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>140</v>
       </c>
@@ -1966,31 +1964,31 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1B00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>141</v>
       </c>
@@ -2010,31 +2008,31 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1C00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>142</v>
       </c>
@@ -2054,31 +2052,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>116</v>
       </c>
@@ -2098,31 +2096,31 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1D00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>143</v>
       </c>
@@ -2142,31 +2140,31 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1E00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>144</v>
       </c>
@@ -2186,31 +2184,31 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1F00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>145</v>
       </c>
@@ -2230,31 +2228,31 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>146</v>
       </c>
@@ -2274,31 +2272,31 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>147</v>
       </c>
@@ -2318,31 +2316,31 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>148</v>
       </c>
@@ -2362,31 +2360,31 @@
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2300-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>149</v>
       </c>
@@ -2406,31 +2404,31 @@
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2400-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>150</v>
       </c>
@@ -2450,31 +2448,31 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>151</v>
       </c>
@@ -2494,31 +2492,31 @@
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2600-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>152</v>
       </c>
@@ -2538,31 +2536,31 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>117</v>
       </c>
@@ -2582,31 +2580,31 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>153</v>
       </c>
@@ -2626,31 +2624,31 @@
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2800-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>154</v>
       </c>
@@ -2670,31 +2668,31 @@
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2900-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>155</v>
       </c>
@@ -2714,31 +2712,31 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2A00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>156</v>
       </c>
@@ -2758,31 +2756,31 @@
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2B00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>157</v>
       </c>
@@ -2802,31 +2800,31 @@
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2C00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>158</v>
       </c>
@@ -2846,31 +2844,31 @@
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2D00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>159</v>
       </c>
@@ -2890,31 +2888,31 @@
 </file>
 
 <file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2E00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>160</v>
       </c>
@@ -2934,31 +2932,31 @@
 </file>
 
 <file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-2F00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>161</v>
       </c>
@@ -2978,31 +2976,31 @@
 </file>
 
 <file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>162</v>
       </c>
@@ -3022,31 +3020,31 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>118</v>
       </c>
@@ -3066,31 +3064,31 @@
 </file>
 
 <file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>163</v>
       </c>
@@ -3110,31 +3108,31 @@
 </file>
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>164</v>
       </c>
@@ -3154,31 +3152,31 @@
 </file>
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3300-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>165</v>
       </c>
@@ -3198,31 +3196,31 @@
 </file>
 
 <file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3400-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>166</v>
       </c>
@@ -3242,31 +3240,31 @@
 </file>
 
 <file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>69</v>
       </c>
@@ -3286,31 +3284,31 @@
 </file>
 
 <file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3600-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>167</v>
       </c>
@@ -3330,31 +3328,31 @@
 </file>
 
 <file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>168</v>
       </c>
@@ -3374,31 +3372,31 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3800-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>169</v>
       </c>
@@ -3418,31 +3416,31 @@
 </file>
 
 <file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3900-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>170</v>
       </c>
@@ -3462,31 +3460,31 @@
 </file>
 
 <file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3A00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>171</v>
       </c>
@@ -3506,31 +3504,31 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>119</v>
       </c>
@@ -3550,31 +3548,31 @@
 </file>
 
 <file path=xl/worksheets/sheet60.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3B00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>172</v>
       </c>
@@ -3594,31 +3592,31 @@
 </file>
 
 <file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3C00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>173</v>
       </c>
@@ -3638,31 +3636,31 @@
 </file>
 
 <file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3D00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>174</v>
       </c>
@@ -3682,31 +3680,31 @@
 </file>
 
 <file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3E00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>174</v>
       </c>
@@ -3726,31 +3724,31 @@
 </file>
 
 <file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-3F00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>175</v>
       </c>
@@ -3770,31 +3768,31 @@
 </file>
 
 <file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>176</v>
       </c>
@@ -3814,31 +3812,31 @@
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>177</v>
       </c>
@@ -3858,31 +3856,31 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>178</v>
       </c>
@@ -3902,31 +3900,31 @@
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4300-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>179</v>
       </c>
@@ -3946,31 +3944,31 @@
 </file>
 
 <file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4400-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>180</v>
       </c>
@@ -3990,31 +3988,31 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>120</v>
       </c>
@@ -4034,31 +4032,31 @@
 </file>
 
 <file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -4078,31 +4076,31 @@
 </file>
 
 <file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4600-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>182</v>
       </c>
@@ -4122,31 +4120,31 @@
 </file>
 
 <file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>183</v>
       </c>
@@ -4166,31 +4164,31 @@
 </file>
 
 <file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4800-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>184</v>
       </c>
@@ -4210,31 +4208,31 @@
 </file>
 
 <file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4900-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>185</v>
       </c>
@@ -4254,31 +4252,31 @@
 </file>
 
 <file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4A00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>186</v>
       </c>
@@ -4298,31 +4296,31 @@
 </file>
 
 <file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4B00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>187</v>
       </c>
@@ -4342,31 +4340,31 @@
 </file>
 
 <file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4C00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>188</v>
       </c>
@@ -4386,31 +4384,31 @@
 </file>
 
 <file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4D00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>189</v>
       </c>
@@ -4430,31 +4428,31 @@
 </file>
 
 <file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4E00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>190</v>
       </c>
@@ -4474,31 +4472,31 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>121</v>
       </c>
@@ -4518,31 +4516,31 @@
 </file>
 
 <file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-4F00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>191</v>
       </c>
@@ -4562,31 +4560,31 @@
 </file>
 
 <file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5000-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>192</v>
       </c>
@@ -4606,31 +4604,31 @@
 </file>
 
 <file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5100-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>193</v>
       </c>
@@ -4650,31 +4648,31 @@
 </file>
 
 <file path=xl/worksheets/sheet83.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5200-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>194</v>
       </c>
@@ -4694,31 +4692,31 @@
 </file>
 
 <file path=xl/worksheets/sheet84.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5300-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>195</v>
       </c>
@@ -4738,31 +4736,31 @@
 </file>
 
 <file path=xl/worksheets/sheet85.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5400-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>196</v>
       </c>
@@ -4782,31 +4780,31 @@
 </file>
 
 <file path=xl/worksheets/sheet86.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5500-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>197</v>
       </c>
@@ -4826,31 +4824,31 @@
 </file>
 
 <file path=xl/worksheets/sheet87.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5600-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>198</v>
       </c>
@@ -4870,31 +4868,31 @@
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5700-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>199</v>
       </c>
@@ -4914,31 +4912,31 @@
 </file>
 
 <file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5800-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>200</v>
       </c>
@@ -4958,31 +4956,31 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
@@ -5002,31 +5000,31 @@
 </file>
 
 <file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5900-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>201</v>
       </c>
@@ -5046,31 +5044,31 @@
 </file>
 
 <file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5A00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>
@@ -5090,31 +5088,31 @@
 </file>
 
 <file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-5B00-000000000000}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="21.95" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="33.950000000000003" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>202</v>
       </c>

--- a/jira_automation/project_documents.xlsx
+++ b/jira_automation/project_documents.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" tabRatio="881" activeTab="11"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11385" tabRatio="678" firstSheet="1" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="HomePage" sheetId="1" r:id="rId1"/>
-    <sheet name="ProjectsPage" sheetId="2" r:id="rId2"/>
+    <sheet name="rr" sheetId="2" r:id="rId2"/>
     <sheet name="ExploreSolutionsPage" sheetId="3" r:id="rId3"/>
     <sheet name="AiSystemsPage" sheetId="4" r:id="rId4"/>
     <sheet name="BlockchainPage" sheetId="5" r:id="rId5"/>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="215">
   <si>
     <t>Title</t>
   </si>
@@ -714,6 +714,42 @@
   </si>
   <si>
     <t>404 Not Found | ECODERS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about us page elements. </t>
+  </si>
+  <si>
+    <t>element name</t>
+  </si>
+  <si>
+    <t>xpath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">css selector </t>
+  </si>
+  <si>
+    <t>about badge</t>
+  </si>
+  <si>
+    <t>span[class = 'service-tag-pill']:nth-of-type(1)   ,  div.service-hero-layout&gt;div&gt;div.service-tag-row&gt;span:nth-of-type(1)</t>
+  </si>
+  <si>
+    <t>span[class = 'service-tag-pill']:nth-of-type(2)   ,  div.service-hero-layout&gt;div&gt;div.service-tag-row&gt;span:nth-of-type(1)</t>
+  </si>
+  <si>
+    <t>software</t>
+  </si>
+  <si>
+    <t>ai system</t>
+  </si>
+  <si>
+    <t>blockchain</t>
+  </si>
+  <si>
+    <t>cloud</t>
+  </si>
+  <si>
+    <t>(//span[@class = 'service-tag-pill'])[1]</t>
   </si>
 </sst>
 </file>
@@ -1217,12 +1253,12 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="55" customWidth="1"/>
-    <col min="3" max="3" width="40" customWidth="1"/>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="55" customWidth="1"/>
+    <col min="3" max="3" width="120.7109375" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1254,6 +1290,65 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B7" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C8" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C9" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="C10" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" t="s">
+        <v>208</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
